--- a/Employee_Reports_wi48/Dennis Delfino Daginotan Q0471.xlsx
+++ b/Employee_Reports_wi48/Dennis Delfino Daginotan Q0471.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-80</v>
+        <v>-83</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-89</v>
+        <v>-92</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -986,11 +986,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
